--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Beer style category: IPA, Pilsner, Seasonal, Sour, Stout, or Wheat.</t>
+          <t>Beer style category: IPA, Pilsner, Specialty, Sour, Stout, or Wheat.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Total CO2 emissions attributable to the batch, in kg.</t>
+          <t>CO2 emissions from purchased electricity for the batch, in kg (scope 2 only; excludes gas, ingredients, and packaging).</t>
         </is>
       </c>
     </row>
